--- a/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T11:03:45+00:00</t>
+    <t>2026-03-06T11:19:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T11:19:51+00:00</t>
+    <t>2026-03-11T07:45:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-slot.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="218">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T07:45:24+00:00</t>
+    <t>2026-04-07T09:25:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -475,6 +475,22 @@
   </si>
   <si>
     <t>An optional URL that can be used for redirects to a webpage for booking an Appointment. It should contain identifying information about the Slot so that it can be preselected on the target booking page.</t>
+  </si>
+  <si>
+    <t>Slot.extension:cancellationPolicy</t>
+  </si>
+  <si>
+    <t>cancellationPolicy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-ext-cancellationPolicy}
+</t>
+  </si>
+  <si>
+    <t>The policy for a cancellation</t>
+  </si>
+  <si>
+    <t>This Extension provides the information about the policy of a cancellation of an appointment. It can contain a time frame until when a cancellation is possible or what the fee for a cancellation will be.</t>
   </si>
   <si>
     <t>Slot.modifierExtension</t>
@@ -972,7 +988,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM23"/>
+  <dimension ref="A1:AM24"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="27.8125" customWidth="true" bestFit="true"/>
@@ -2241,43 +2257,41 @@
         <v>148</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>130</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="D12" t="s" s="2">
-        <v>149</v>
+        <v>18</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N12" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="O12" t="s" s="2">
-        <v>153</v>
-      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>18</v>
       </c>
@@ -2325,7 +2339,7 @@
         <v>18</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2343,7 +2357,7 @@
         <v>18</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>129</v>
+        <v>18</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>18</v>
@@ -2351,14 +2365,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>18</v>
+        <v>154</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2371,22 +2385,26 @@
         <v>18</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="O13" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>18</v>
       </c>
@@ -2434,7 +2452,7 @@
         <v>18</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2446,13 +2464,13 @@
         <v>18</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>159</v>
+        <v>18</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>18</v>
+        <v>129</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>18</v>
@@ -2519,11 +2537,13 @@
         <v>18</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="Y14" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>18</v>
+      </c>
       <c r="Z14" t="s" s="2">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>18</v>
@@ -2556,7 +2576,7 @@
         <v>96</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>18</v>
@@ -2567,10 +2587,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2593,13 +2613,13 @@
         <v>85</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2626,11 +2646,11 @@
         <v>18</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>18</v>
@@ -2648,7 +2668,7 @@
         <v>18</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -2663,7 +2683,7 @@
         <v>96</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>18</v>
@@ -2674,10 +2694,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2700,7 +2720,7 @@
         <v>85</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>174</v>
@@ -2735,12 +2755,10 @@
       <c r="X16" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Y16" s="2"/>
+      <c r="Z16" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="Z16" t="s" s="2">
-        <v>178</v>
-      </c>
       <c r="AA16" t="s" s="2">
         <v>18</v>
       </c>
@@ -2757,7 +2775,7 @@
         <v>18</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>74</v>
@@ -2772,7 +2790,7 @@
         <v>96</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>18</v>
@@ -2783,10 +2801,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2809,17 +2827,15 @@
         <v>85</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="M17" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>182</v>
-      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>18</v>
@@ -2844,9 +2860,11 @@
         <v>18</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Y17" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="Z17" t="s" s="2">
         <v>183</v>
       </c>
@@ -2866,7 +2884,7 @@
         <v>18</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -2881,7 +2899,7 @@
         <v>96</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>18</v>
@@ -2903,10 +2921,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>18</v>
@@ -2918,15 +2936,17 @@
         <v>85</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>18</v>
@@ -2951,13 +2971,11 @@
         <v>18</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>18</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="Y18" s="2"/>
       <c r="Z18" t="s" s="2">
-        <v>18</v>
+        <v>188</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>18</v>
@@ -2978,10 +2996,10 @@
         <v>184</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>18</v>
@@ -2990,7 +3008,7 @@
         <v>96</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>18</v>
+        <v>171</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>18</v>
@@ -3001,10 +3019,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3027,13 +3045,13 @@
         <v>85</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>104</v>
+        <v>190</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3060,13 +3078,13 @@
         <v>18</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>108</v>
+        <v>18</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>191</v>
+        <v>18</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>192</v>
+        <v>18</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>18</v>
@@ -3084,7 +3102,7 @@
         <v>18</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>84</v>
@@ -3105,15 +3123,15 @@
         <v>18</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>193</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3136,13 +3154,13 @@
         <v>85</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3169,13 +3187,13 @@
         <v>18</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>18</v>
+        <v>196</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>18</v>
+        <v>197</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>18</v>
@@ -3193,7 +3211,7 @@
         <v>18</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>84</v>
@@ -3208,21 +3226,21 @@
         <v>96</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>199</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3245,7 +3263,7 @@
         <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>201</v>
@@ -3302,7 +3320,7 @@
         <v>18</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>84</v>
@@ -3317,21 +3335,21 @@
         <v>96</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3339,7 +3357,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>84</v>
@@ -3351,10 +3369,10 @@
         <v>18</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>206</v>
@@ -3367,9 +3385,7 @@
       <c r="P22" t="s" s="2">
         <v>18</v>
       </c>
-      <c r="Q22" t="s" s="2">
-        <v>208</v>
-      </c>
+      <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
         <v>18</v>
       </c>
@@ -3413,10 +3429,10 @@
         <v>18</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>84</v>
@@ -3428,13 +3444,13 @@
         <v>96</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>18</v>
+        <v>203</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>18</v>
+        <v>208</v>
       </c>
     </row>
     <row r="23">
@@ -3478,7 +3494,9 @@
       <c r="P23" t="s" s="2">
         <v>18</v>
       </c>
-      <c r="Q23" s="2"/>
+      <c r="Q23" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="R23" t="s" s="2">
         <v>18</v>
       </c>
@@ -3543,6 +3561,115 @@
         <v>18</v>
       </c>
       <c r="AM23" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q24" s="2"/>
+      <c r="R24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>18</v>
       </c>
     </row>

--- a/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T09:25:26+00:00</t>
+    <t>2026-04-07T09:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T09:46:48+00:00</t>
+    <t>2026-06-09T10:31:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T10:31:34+00:00</t>
+    <t>2026-06-09T10:57:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T10:57:01+00:00</t>
+    <t>2026-06-09T12:42:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
